--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>780</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1072,7 +1072,7 @@
       </x:c>
       <x:c r="C17" s="12" t="s"/>
       <x:c r="D17" s="18" t="n">
-        <x:v>2320</x:v>
+        <x:v>2720</x:v>
       </x:c>
       <x:c r="E17" s="8" t="s"/>
       <x:c r="F17" s="1" t="s"/>
@@ -1151,7 +1151,7 @@
       </x:c>
       <x:c r="C20" s="12" t="s"/>
       <x:c r="D20" s="17" t="n">
-        <x:v>22930</x:v>
+        <x:v>29680</x:v>
       </x:c>
       <x:c r="E20" s="8" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>28260</x:v>
+        <x:v>35760</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>
@@ -1305,7 +1305,7 @@
       </x:c>
       <x:c r="C26" s="12" t="s"/>
       <x:c r="D26" s="8" t="n">
-        <x:v>350</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="E26" s="8" t="s"/>
       <x:c r="F26" s="1" t="s"/>
@@ -1332,7 +1332,7 @@
       </x:c>
       <x:c r="C27" s="12" t="s"/>
       <x:c r="D27" s="18" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E27" s="8" t="s"/>
       <x:c r="F27" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>1080</x:v>
+        <x:v>1110</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>35760</x:v>
+        <x:v>37260</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>1110</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1072,7 +1072,7 @@
       </x:c>
       <x:c r="C17" s="12" t="s"/>
       <x:c r="D17" s="18" t="n">
-        <x:v>2720</x:v>
+        <x:v>2320</x:v>
       </x:c>
       <x:c r="E17" s="8" t="s"/>
       <x:c r="F17" s="1" t="s"/>
@@ -1151,7 +1151,7 @@
       </x:c>
       <x:c r="C20" s="12" t="s"/>
       <x:c r="D20" s="17" t="n">
-        <x:v>29680</x:v>
+        <x:v>22930</x:v>
       </x:c>
       <x:c r="E20" s="8" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>37260</x:v>
+        <x:v>29760</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>
@@ -1305,7 +1305,7 @@
       </x:c>
       <x:c r="C26" s="12" t="s"/>
       <x:c r="D26" s="8" t="n">
-        <x:v>650</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E26" s="8" t="s"/>
       <x:c r="F26" s="1" t="s"/>
@@ -1332,7 +1332,7 @@
       </x:c>
       <x:c r="C27" s="12" t="s"/>
       <x:c r="D27" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E27" s="8" t="s"/>
       <x:c r="F27" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -27,7 +27,7 @@
     <x:t>AND INCOME DEPOSITED WITH THE BUREAU OF TREASURY</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">FOR THE MONTH OF </x:t>
+    <x:t>FOR THE MONTH OF March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Department of Information and Communications Technology</x:t>
@@ -124,7 +124,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11.0"/>
       <x:color theme="1"/>
@@ -147,6 +147,14 @@
       <x:sz val="10.0"/>
       <x:color theme="1"/>
       <x:name val="Tahoma"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="14"/>
+      <x:color theme="1"/>
+      <x:name val="Tahoma"/>
+      <x:family val="2"/>
     </x:font>
   </x:fonts>
   <x:fills count="3">
@@ -304,7 +312,7 @@
       </x:bottom>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="21">
+  <x:cellStyleXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -313,6 +321,12 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -367,7 +381,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -440,6 +454,14 @@
     </x:xf>
     <x:xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -711,12 +733,12 @@
     </x:row>
     <x:row r="3" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A3" s="1" t="s"/>
-      <x:c r="B3" s="2" t="s">
+      <x:c r="B3" s="27" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
+      <x:c r="C3" s="28" t="s"/>
+      <x:c r="D3" s="28" t="s"/>
+      <x:c r="E3" s="28" t="s"/>
       <x:c r="F3" s="1" t="s"/>
       <x:c r="G3" s="1" t="s"/>
       <x:c r="H3" s="1" t="s"/>
@@ -967,10 +989,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="12" t="s"/>
-      <x:c r="D13" s="8" t="n">
+      <x:c r="D13" s="8" t="s"/>
+      <x:c r="E13" s="17" t="n">
         <x:v>810</x:v>
       </x:c>
-      <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
       <x:c r="G13" s="1" t="s"/>
       <x:c r="H13" s="1" t="s"/>
@@ -1431,8 +1453,12 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C31" s="8" t="s"/>
-      <x:c r="D31" s="20" t="s"/>
-      <x:c r="E31" s="20" t="s"/>
+      <x:c r="D31" s="20">
+        <x:f>SUM(D10:D29)</x:f>
+      </x:c>
+      <x:c r="E31" s="20">
+        <x:f>SUM(E13)</x:f>
+      </x:c>
       <x:c r="F31" s="1" t="s"/>
       <x:c r="G31" s="1" t="s"/>
       <x:c r="H31" s="21" t="s">

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -11,15 +11,15 @@
   <x:definedNames/>
   <x:calcPr/>
   <x:extLst>
-    <x:ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7mgj0RW+M/c4oZNFRRXIaoU8wSKM+g=="/>
+    <x:ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="COD0aEwbTl9foRQai37wWpsswXIcthiPZBvWn6d4x4U="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <x:si>
     <x:t>MONTHLY REPORT OF INCOME COLLECTED</x:t>
   </x:si>
@@ -66,22 +66,43 @@
     <x:t>Permit Fees</x:t>
   </x:si>
   <x:si>
+    <x:t>4-02-01-010</x:t>
+  </x:si>
+  <x:si>
     <x:t>Registration Fees</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4-02-01-020</x:t>
   </x:si>
   <x:si>
     <x:t>Clearance and Certification Fees</x:t>
   </x:si>
   <x:si>
+    <x:t>4-02-01-040</x:t>
+  </x:si>
+  <x:si>
     <x:t>Licensing Fees</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4-02-01-060</x:t>
   </x:si>
   <x:si>
     <x:t>Supervision &amp; Regulation Enforcement Fees</x:t>
   </x:si>
   <x:si>
+    <x:t>4-02-01-070</x:t>
+  </x:si>
+  <x:si>
     <x:t>Spectrum Usage Fees</x:t>
   </x:si>
   <x:si>
+    <x:t>4-02-01-080</x:t>
+  </x:si>
+  <x:si>
     <x:t>Inspections Fees</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4-02-02-100</x:t>
   </x:si>
   <x:si>
     <x:t>Verification &amp; Aunthentication Fees</x:t>
@@ -90,10 +111,19 @@
     <x:t>Processing Fees</x:t>
   </x:si>
   <x:si>
+    <x:t>4-02-01-130</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fines and Penalties - Service Income</x:t>
   </x:si>
   <x:si>
+    <x:t>4-02-01-140</x:t>
+  </x:si>
+  <x:si>
     <x:t>Other Service Income</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4-02-01-990</x:t>
   </x:si>
   <x:si>
     <x:t>Examination Fees</x:t>
@@ -105,7 +135,13 @@
     <x:t>Other Non-Operating Income</x:t>
   </x:si>
   <x:si>
+    <x:t>4-06-01-010</x:t>
+  </x:si>
+  <x:si>
     <x:t>Miscellaneous Income</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4-06-09-990</x:t>
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
@@ -116,6 +152,24 @@
   <x:si>
     <x:t>Certified Correct:</x:t>
   </x:si>
+  <x:si>
+    <x:t>Noted By:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Accountant Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Regional Director/OIC Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Position</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Date </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Date</x:t>
+  </x:si>
 </x:sst>
 </file>
 
@@ -124,7 +178,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11.0"/>
       <x:color theme="1"/>
@@ -149,6 +203,26 @@
       <x:name val="Tahoma"/>
     </x:font>
     <x:font>
+      <x:sz val="11.0"/>
+      <x:color theme="1"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12.0"/>
+      <x:color theme="1"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="12.0"/>
+      <x:color theme="1"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:color theme="1"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
@@ -168,7 +242,7 @@
       <x:patternFill patternType="gray125"/>
     </x:fill>
   </x:fills>
-  <x:borders count="13">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:left style="medium">
@@ -287,6 +361,20 @@
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
       <x:left style="medium">
         <x:color rgb="FFCCCCCC"/>
       </x:left>
@@ -312,7 +400,7 @@
       </x:bottom>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -323,10 +411,10 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -362,26 +450,44 @@
     <x:xf numFmtId="4" fontId="4" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="4" fontId="2" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="4" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -392,9 +498,6 @@
       <x:alignment horizontal="center" wrapText="1" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1" shrinkToFit="0" readingOrder="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -430,6 +533,9 @@
     <x:xf numFmtId="4" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" wrapText="1" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" wrapText="1" shrinkToFit="0"/>
     </x:xf>
@@ -442,25 +548,41 @@
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="bottom" readingOrder="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -733,12 +855,12 @@
     </x:row>
     <x:row r="3" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A3" s="1" t="s"/>
-      <x:c r="B3" s="27" t="s">
+      <x:c r="B3" s="31" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="28" t="s"/>
-      <x:c r="D3" s="28" t="s"/>
-      <x:c r="E3" s="28" t="s"/>
+      <x:c r="C3" s="32" t="s"/>
+      <x:c r="D3" s="32" t="s"/>
+      <x:c r="E3" s="32" t="s"/>
       <x:c r="F3" s="1" t="s"/>
       <x:c r="G3" s="1" t="s"/>
       <x:c r="H3" s="1" t="s"/>
@@ -781,7 +903,7 @@
     </x:row>
     <x:row r="5" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A5" s="1" t="s"/>
-      <x:c r="B5" s="5" t="s">
+      <x:c r="B5" s="4" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s"/>
@@ -806,7 +928,7 @@
     </x:row>
     <x:row r="6" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A6" s="1" t="s"/>
-      <x:c r="B6" s="6" t="s">
+      <x:c r="B6" s="5" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s"/>
@@ -854,10 +976,10 @@
     </x:row>
     <x:row r="8" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A8" s="1" t="s"/>
-      <x:c r="B8" s="7" t="s"/>
-      <x:c r="C8" s="7" t="s"/>
-      <x:c r="D8" s="7" t="s"/>
-      <x:c r="E8" s="7" t="s"/>
+      <x:c r="B8" s="6" t="s"/>
+      <x:c r="C8" s="6" t="s"/>
+      <x:c r="D8" s="6" t="s"/>
+      <x:c r="E8" s="6" t="s"/>
       <x:c r="F8" s="1" t="s"/>
       <x:c r="G8" s="1" t="s"/>
       <x:c r="H8" s="1" t="s"/>
@@ -876,13 +998,13 @@
       <x:c r="U8" s="1" t="s"/>
     </x:row>
     <x:row r="9" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A9" s="8" t="s"/>
-      <x:c r="B9" s="8" t="s"/>
-      <x:c r="C9" s="8" t="s"/>
-      <x:c r="D9" s="9" t="s">
+      <x:c r="A9" s="7" t="s"/>
+      <x:c r="B9" s="7" t="s"/>
+      <x:c r="C9" s="7" t="s"/>
+      <x:c r="D9" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E9" s="10" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
       <x:c r="F9" s="1" t="s"/>
       <x:c r="G9" s="1" t="s"/>
       <x:c r="H9" s="1" t="s"/>
@@ -901,17 +1023,17 @@
       <x:c r="U9" s="1" t="s"/>
     </x:row>
     <x:row r="10" spans="1:26" ht="27" customHeight="1">
-      <x:c r="A10" s="8" t="s"/>
-      <x:c r="B10" s="11" t="s">
+      <x:c r="A10" s="7" t="s"/>
+      <x:c r="B10" s="10" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C10" s="12" t="s">
+      <x:c r="C10" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D10" s="8" t="s">
+      <x:c r="D10" s="7" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E10" s="13" t="s">
+      <x:c r="E10" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s"/>
@@ -932,15 +1054,15 @@
       <x:c r="U10" s="1" t="s"/>
     </x:row>
     <x:row r="11" spans="1:26" ht="17.25" customHeight="1">
-      <x:c r="A11" s="8" t="s"/>
-      <x:c r="B11" s="14" t="s"/>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="A11" s="7" t="s"/>
+      <x:c r="B11" s="13" t="s"/>
+      <x:c r="C11" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
+      <x:c r="D11" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s"/>
       <x:c r="F11" s="1" t="s"/>
       <x:c r="G11" s="1" t="s"/>
       <x:c r="H11" s="1" t="s"/>
@@ -959,13 +1081,13 @@
       <x:c r="U11" s="1" t="s"/>
     </x:row>
     <x:row r="12" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A12" s="8" t="s"/>
-      <x:c r="B12" s="11" t="s">
+      <x:c r="A12" s="7" t="s"/>
+      <x:c r="B12" s="10" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C12" s="8" t="s"/>
-      <x:c r="D12" s="8" t="s"/>
-      <x:c r="E12" s="11" t="s"/>
+      <x:c r="C12" s="7" t="s"/>
+      <x:c r="D12" s="7" t="s"/>
+      <x:c r="E12" s="10" t="s"/>
       <x:c r="F12" s="1" t="s"/>
       <x:c r="G12" s="1" t="s"/>
       <x:c r="H12" s="1" t="s"/>
@@ -984,13 +1106,13 @@
       <x:c r="U12" s="1" t="s"/>
     </x:row>
     <x:row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A13" s="8" t="s"/>
-      <x:c r="B13" s="11" t="s">
+      <x:c r="A13" s="7" t="s"/>
+      <x:c r="B13" s="10" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="12" t="s"/>
-      <x:c r="D13" s="8" t="s"/>
-      <x:c r="E13" s="17" t="n">
+      <x:c r="C13" s="11" t="s"/>
+      <x:c r="D13" s="7" t="s"/>
+      <x:c r="E13" s="16" t="n">
         <x:v>810</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
@@ -1011,11 +1133,11 @@
       <x:c r="U13" s="1" t="s"/>
     </x:row>
     <x:row r="14" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A14" s="8" t="s"/>
-      <x:c r="B14" s="11" t="s"/>
-      <x:c r="C14" s="12" t="s"/>
-      <x:c r="D14" s="8" t="s"/>
-      <x:c r="E14" s="8" t="s"/>
+      <x:c r="A14" s="7" t="s"/>
+      <x:c r="B14" s="10" t="s"/>
+      <x:c r="C14" s="11" t="s"/>
+      <x:c r="D14" s="7" t="s"/>
+      <x:c r="E14" s="7" t="s"/>
       <x:c r="F14" s="1" t="s"/>
       <x:c r="G14" s="1" t="s"/>
       <x:c r="H14" s="1" t="s"/>
@@ -1034,15 +1156,17 @@
       <x:c r="U14" s="1" t="s"/>
     </x:row>
     <x:row r="15" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A15" s="8" t="s"/>
-      <x:c r="B15" s="11" t="s">
+      <x:c r="A15" s="7" t="s"/>
+      <x:c r="B15" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="12" t="s"/>
-      <x:c r="D15" s="17" t="n">
+      <x:c r="C15" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="8" t="s"/>
+      <x:c r="E15" s="7" t="s"/>
       <x:c r="F15" s="1" t="s"/>
       <x:c r="G15" s="1" t="s"/>
       <x:c r="H15" s="1" t="s"/>
@@ -1061,15 +1185,17 @@
       <x:c r="U15" s="1" t="s"/>
     </x:row>
     <x:row r="16" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A16" s="8" t="s"/>
-      <x:c r="B16" s="11" t="s">
-        <x:v>15</x:v>
+      <x:c r="A16" s="7" t="s"/>
+      <x:c r="B16" s="10" t="s">
+        <x:v>16</x:v>
       </x:c>
-      <x:c r="C16" s="12" t="s"/>
-      <x:c r="D16" s="17" t="n">
+      <x:c r="C16" s="17" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="8" t="s"/>
+      <x:c r="E16" s="7" t="s"/>
       <x:c r="F16" s="1" t="s"/>
       <x:c r="G16" s="1" t="s"/>
       <x:c r="H16" s="1" t="s"/>
@@ -1088,15 +1214,17 @@
       <x:c r="U16" s="1" t="s"/>
     </x:row>
     <x:row r="17" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A17" s="8" t="s"/>
-      <x:c r="B17" s="11" t="s">
-        <x:v>16</x:v>
+      <x:c r="A17" s="7" t="s"/>
+      <x:c r="B17" s="10" t="s">
+        <x:v>18</x:v>
       </x:c>
-      <x:c r="C17" s="12" t="s"/>
+      <x:c r="C17" s="17" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="D17" s="18" t="n">
         <x:v>2320</x:v>
       </x:c>
-      <x:c r="E17" s="8" t="s"/>
+      <x:c r="E17" s="7" t="s"/>
       <x:c r="F17" s="1" t="s"/>
       <x:c r="G17" s="1" t="s"/>
       <x:c r="H17" s="1" t="s"/>
@@ -1115,15 +1243,17 @@
       <x:c r="U17" s="1" t="s"/>
     </x:row>
     <x:row r="18" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A18" s="8" t="s"/>
-      <x:c r="B18" s="11" t="s">
-        <x:v>17</x:v>
+      <x:c r="A18" s="7" t="s"/>
+      <x:c r="B18" s="10" t="s">
+        <x:v>20</x:v>
       </x:c>
-      <x:c r="C18" s="12" t="s"/>
-      <x:c r="D18" s="17" t="n">
+      <x:c r="C18" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="8" t="s"/>
+      <x:c r="E18" s="7" t="s"/>
       <x:c r="F18" s="1" t="s"/>
       <x:c r="G18" s="1" t="s"/>
       <x:c r="H18" s="1" t="s"/>
@@ -1142,13 +1272,15 @@
       <x:c r="U18" s="1" t="s"/>
     </x:row>
     <x:row r="19" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A19" s="8" t="s"/>
-      <x:c r="B19" s="11" t="s">
-        <x:v>18</x:v>
+      <x:c r="A19" s="7" t="s"/>
+      <x:c r="B19" s="10" t="s">
+        <x:v>22</x:v>
       </x:c>
-      <x:c r="C19" s="12" t="s"/>
-      <x:c r="D19" s="17" t="s"/>
-      <x:c r="E19" s="8" t="s"/>
+      <x:c r="C19" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s"/>
+      <x:c r="E19" s="7" t="s"/>
       <x:c r="F19" s="1" t="s"/>
       <x:c r="G19" s="1" t="s"/>
       <x:c r="H19" s="1" t="s"/>
@@ -1167,15 +1299,17 @@
       <x:c r="U19" s="1" t="s"/>
     </x:row>
     <x:row r="20" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A20" s="8" t="s"/>
-      <x:c r="B20" s="11" t="s">
-        <x:v>19</x:v>
+      <x:c r="A20" s="7" t="s"/>
+      <x:c r="B20" s="10" t="s">
+        <x:v>24</x:v>
       </x:c>
-      <x:c r="C20" s="12" t="s"/>
-      <x:c r="D20" s="17" t="n">
+      <x:c r="C20" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="n">
         <x:v>22930</x:v>
       </x:c>
-      <x:c r="E20" s="8" t="s"/>
+      <x:c r="E20" s="7" t="s"/>
       <x:c r="F20" s="1" t="s"/>
       <x:c r="G20" s="1" t="s"/>
       <x:c r="H20" s="1" t="s"/>
@@ -1194,15 +1328,17 @@
       <x:c r="U20" s="1" t="s"/>
     </x:row>
     <x:row r="21" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A21" s="8" t="s"/>
-      <x:c r="B21" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="A21" s="7" t="s"/>
+      <x:c r="B21" s="10" t="s">
+        <x:v>26</x:v>
       </x:c>
-      <x:c r="C21" s="12" t="s"/>
-      <x:c r="D21" s="17" t="n">
+      <x:c r="C21" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="n">
         <x:v>29760</x:v>
       </x:c>
-      <x:c r="E21" s="8" t="s"/>
+      <x:c r="E21" s="7" t="s"/>
       <x:c r="F21" s="1" t="s"/>
       <x:c r="G21" s="1" t="s"/>
       <x:c r="H21" s="1" t="s"/>
@@ -1221,13 +1357,12 @@
       <x:c r="U21" s="1" t="s"/>
     </x:row>
     <x:row r="22" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A22" s="8" t="s"/>
-      <x:c r="B22" s="11" t="s">
-        <x:v>21</x:v>
+      <x:c r="A22" s="7" t="s"/>
+      <x:c r="B22" s="10" t="s">
+        <x:v>28</x:v>
       </x:c>
-      <x:c r="C22" s="12" t="s"/>
       <x:c r="D22" s="18" t="s"/>
-      <x:c r="E22" s="8" t="s"/>
+      <x:c r="E22" s="7" t="s"/>
       <x:c r="F22" s="1" t="s"/>
       <x:c r="G22" s="1" t="s"/>
       <x:c r="H22" s="1" t="s"/>
@@ -1246,13 +1381,15 @@
       <x:c r="U22" s="1" t="s"/>
     </x:row>
     <x:row r="23" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A23" s="8" t="s"/>
-      <x:c r="B23" s="11" t="s">
-        <x:v>22</x:v>
+      <x:c r="A23" s="7" t="s"/>
+      <x:c r="B23" s="10" t="s">
+        <x:v>29</x:v>
       </x:c>
-      <x:c r="C23" s="12" t="s"/>
-      <x:c r="D23" s="17" t="s"/>
-      <x:c r="E23" s="8" t="s"/>
+      <x:c r="C23" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s"/>
+      <x:c r="E23" s="7" t="s"/>
       <x:c r="F23" s="1" t="s"/>
       <x:c r="G23" s="1" t="s"/>
       <x:c r="H23" s="1" t="s"/>
@@ -1271,13 +1408,15 @@
       <x:c r="U23" s="1" t="s"/>
     </x:row>
     <x:row r="24" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A24" s="8" t="s"/>
-      <x:c r="B24" s="11" t="s">
-        <x:v>23</x:v>
+      <x:c r="A24" s="7" t="s"/>
+      <x:c r="B24" s="10" t="s">
+        <x:v>31</x:v>
       </x:c>
-      <x:c r="C24" s="12" t="s"/>
-      <x:c r="D24" s="17" t="s"/>
-      <x:c r="E24" s="8" t="s"/>
+      <x:c r="C24" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s"/>
+      <x:c r="E24" s="7" t="s"/>
       <x:c r="F24" s="1" t="s"/>
       <x:c r="G24" s="1" t="s"/>
       <x:c r="H24" s="1" t="s"/>
@@ -1296,13 +1435,15 @@
       <x:c r="U24" s="1" t="s"/>
     </x:row>
     <x:row r="25" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A25" s="8" t="s"/>
-      <x:c r="B25" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="A25" s="7" t="s"/>
+      <x:c r="B25" s="10" t="s">
+        <x:v>33</x:v>
       </x:c>
-      <x:c r="C25" s="12" t="s"/>
+      <x:c r="C25" s="17" t="s">
+        <x:v>34</x:v>
+      </x:c>
       <x:c r="D25" s="18" t="s"/>
-      <x:c r="E25" s="8" t="s"/>
+      <x:c r="E25" s="7" t="s"/>
       <x:c r="F25" s="1" t="s"/>
       <x:c r="G25" s="1" t="s"/>
       <x:c r="H25" s="1" t="s"/>
@@ -1321,15 +1462,14 @@
       <x:c r="U25" s="1" t="s"/>
     </x:row>
     <x:row r="26" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A26" s="8" t="s"/>
-      <x:c r="B26" s="11" t="s">
-        <x:v>25</x:v>
+      <x:c r="A26" s="7" t="s"/>
+      <x:c r="B26" s="10" t="s">
+        <x:v>35</x:v>
       </x:c>
-      <x:c r="C26" s="12" t="s"/>
-      <x:c r="D26" s="8" t="n">
+      <x:c r="D26" s="7" t="n">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="E26" s="8" t="s"/>
+      <x:c r="E26" s="7" t="s"/>
       <x:c r="F26" s="1" t="s"/>
       <x:c r="G26" s="1" t="s"/>
       <x:c r="H26" s="1" t="s"/>
@@ -1348,15 +1488,14 @@
       <x:c r="U26" s="1" t="s"/>
     </x:row>
     <x:row r="27" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A27" s="8" t="s"/>
-      <x:c r="B27" s="11" t="s">
-        <x:v>26</x:v>
+      <x:c r="A27" s="7" t="s"/>
+      <x:c r="B27" s="10" t="s">
+        <x:v>36</x:v>
       </x:c>
-      <x:c r="C27" s="12" t="s"/>
       <x:c r="D27" s="18" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E27" s="8" t="s"/>
+      <x:c r="E27" s="7" t="s"/>
       <x:c r="F27" s="1" t="s"/>
       <x:c r="G27" s="1" t="s"/>
       <x:c r="H27" s="1" t="s"/>
@@ -1375,13 +1514,15 @@
       <x:c r="U27" s="1" t="s"/>
     </x:row>
     <x:row r="28" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A28" s="8" t="s"/>
-      <x:c r="B28" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="A28" s="7" t="s"/>
+      <x:c r="B28" s="10" t="s">
+        <x:v>37</x:v>
       </x:c>
-      <x:c r="C28" s="12" t="s"/>
-      <x:c r="D28" s="8" t="s"/>
-      <x:c r="E28" s="8" t="s"/>
+      <x:c r="C28" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D28" s="7" t="s"/>
+      <x:c r="E28" s="7" t="s"/>
       <x:c r="F28" s="1" t="s"/>
       <x:c r="G28" s="1" t="s"/>
       <x:c r="H28" s="1" t="s"/>
@@ -1400,13 +1541,15 @@
       <x:c r="U28" s="1" t="s"/>
     </x:row>
     <x:row r="29" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A29" s="8" t="s"/>
-      <x:c r="B29" s="11" t="s">
-        <x:v>28</x:v>
+      <x:c r="A29" s="7" t="s"/>
+      <x:c r="B29" s="10" t="s">
+        <x:v>39</x:v>
       </x:c>
-      <x:c r="C29" s="12" t="s"/>
-      <x:c r="D29" s="17" t="s"/>
-      <x:c r="E29" s="8" t="s"/>
+      <x:c r="C29" s="17" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D29" s="16" t="s"/>
+      <x:c r="E29" s="7" t="s"/>
       <x:c r="F29" s="1" t="s"/>
       <x:c r="G29" s="1" t="s"/>
       <x:c r="H29" s="1" t="s"/>
@@ -1425,11 +1568,11 @@
       <x:c r="U29" s="1" t="s"/>
     </x:row>
     <x:row r="30" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A30" s="8" t="s"/>
-      <x:c r="B30" s="14" t="s"/>
-      <x:c r="C30" s="14" t="s"/>
+      <x:c r="A30" s="7" t="s"/>
+      <x:c r="B30" s="13" t="s"/>
+      <x:c r="C30" s="13" t="s"/>
       <x:c r="D30" s="19" t="s"/>
-      <x:c r="E30" s="14" t="s"/>
+      <x:c r="E30" s="13" t="s"/>
       <x:c r="F30" s="1" t="s"/>
       <x:c r="G30" s="1" t="s"/>
       <x:c r="H30" s="1" t="s"/>
@@ -1448,11 +1591,11 @@
       <x:c r="U30" s="1" t="s"/>
     </x:row>
     <x:row r="31" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A31" s="8" t="s"/>
-      <x:c r="B31" s="12" t="s">
-        <x:v>29</x:v>
+      <x:c r="A31" s="7" t="s"/>
+      <x:c r="B31" s="11" t="s">
+        <x:v>41</x:v>
       </x:c>
-      <x:c r="C31" s="8" t="s"/>
+      <x:c r="C31" s="7" t="s"/>
       <x:c r="D31" s="20">
         <x:f>SUM(D10:D29)</x:f>
       </x:c>
@@ -1462,7 +1605,7 @@
       <x:c r="F31" s="1" t="s"/>
       <x:c r="G31" s="1" t="s"/>
       <x:c r="H31" s="21" t="s">
-        <x:v>30</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I31" s="1" t="s"/>
       <x:c r="J31" s="1" t="s"/>
@@ -1479,9 +1622,9 @@
       <x:c r="U31" s="1" t="s"/>
     </x:row>
     <x:row r="32" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A32" s="8" t="s"/>
-      <x:c r="B32" s="11" t="s"/>
-      <x:c r="C32" s="11" t="s"/>
+      <x:c r="A32" s="7" t="s"/>
+      <x:c r="B32" s="10" t="s"/>
+      <x:c r="C32" s="10" t="s"/>
       <x:c r="D32" s="22" t="s"/>
       <x:c r="E32" s="22" t="s"/>
       <x:c r="F32" s="1" t="s"/>
@@ -1502,11 +1645,11 @@
       <x:c r="U32" s="1" t="s"/>
     </x:row>
     <x:row r="33" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A33" s="8" t="s"/>
-      <x:c r="B33" s="14" t="s"/>
-      <x:c r="C33" s="14" t="s"/>
+      <x:c r="A33" s="7" t="s"/>
+      <x:c r="B33" s="13" t="s"/>
+      <x:c r="C33" s="13" t="s"/>
       <x:c r="D33" s="19" t="s"/>
-      <x:c r="E33" s="14" t="s"/>
+      <x:c r="E33" s="13" t="s"/>
       <x:c r="F33" s="1" t="s"/>
       <x:c r="G33" s="1" t="s"/>
       <x:c r="H33" s="1" t="s"/>
@@ -1550,10 +1693,12 @@
     <x:row r="35" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A35" s="1" t="s"/>
       <x:c r="B35" s="23" t="s">
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C35" s="24" t="s"/>
-      <x:c r="D35" s="1" t="s"/>
+      <x:c r="D35" s="25" t="s">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="E35" s="1" t="s"/>
       <x:c r="F35" s="1" t="s"/>
       <x:c r="G35" s="1" t="s"/>
@@ -1574,9 +1719,13 @@
     </x:row>
     <x:row r="36" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A36" s="1" t="s"/>
-      <x:c r="B36" s="25" t="s"/>
+      <x:c r="B36" s="26" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="C36" s="1" t="s"/>
-      <x:c r="D36" s="1" t="s"/>
+      <x:c r="D36" s="33" t="s">
+        <x:v>46</x:v>
+      </x:c>
       <x:c r="E36" s="1" t="s"/>
       <x:c r="F36" s="1" t="s"/>
       <x:c r="G36" s="1" t="s"/>
@@ -1597,9 +1746,13 @@
     </x:row>
     <x:row r="37" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A37" s="1" t="s"/>
-      <x:c r="B37" s="25" t="s"/>
+      <x:c r="B37" s="26" t="s">
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="C37" s="1" t="s"/>
-      <x:c r="D37" s="1" t="s"/>
+      <x:c r="D37" s="26" t="s">
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="E37" s="1" t="s"/>
       <x:c r="F37" s="1" t="s"/>
       <x:c r="G37" s="1" t="s"/>
@@ -1620,9 +1773,13 @@
     </x:row>
     <x:row r="38" spans="1:26" ht="26.25" customHeight="1">
       <x:c r="A38" s="1" t="s"/>
-      <x:c r="B38" s="23" t="s"/>
-      <x:c r="C38" s="24" t="s"/>
-      <x:c r="D38" s="1" t="s"/>
+      <x:c r="B38" s="26" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C38" s="28" t="s"/>
+      <x:c r="D38" s="26" t="s">
+        <x:v>49</x:v>
+      </x:c>
       <x:c r="E38" s="1" t="s"/>
       <x:c r="F38" s="1" t="s"/>
       <x:c r="G38" s="1" t="s"/>
@@ -1643,9 +1800,8 @@
     </x:row>
     <x:row r="39" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A39" s="1" t="s"/>
-      <x:c r="B39" s="23" t="s"/>
+      <x:c r="B39" s="29" t="s"/>
       <x:c r="C39" s="24" t="s"/>
-      <x:c r="D39" s="1" t="s"/>
       <x:c r="E39" s="1" t="s"/>
       <x:c r="F39" s="1" t="s"/>
       <x:c r="G39" s="1" t="s"/>
@@ -1666,9 +1822,8 @@
     </x:row>
     <x:row r="40" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A40" s="1" t="s"/>
-      <x:c r="B40" s="26" t="s"/>
+      <x:c r="B40" s="30" t="s"/>
       <x:c r="C40" s="24" t="s"/>
-      <x:c r="D40" s="1" t="s"/>
       <x:c r="E40" s="1" t="s"/>
       <x:c r="F40" s="1" t="s"/>
       <x:c r="G40" s="1" t="s"/>
@@ -7048,14 +7203,13 @@
     <x:row r="999" spans="1:26" ht="14.25" customHeight="1"/>
     <x:row r="1000" spans="1:26" ht="14.25" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="8">
     <x:mergeCell ref="B1:E1"/>
     <x:mergeCell ref="B2:E2"/>
     <x:mergeCell ref="B3:E3"/>
     <x:mergeCell ref="D9:E9"/>
     <x:mergeCell ref="E10:E11"/>
     <x:mergeCell ref="B35:C35"/>
-    <x:mergeCell ref="B38:C38"/>
     <x:mergeCell ref="B39:C39"/>
     <x:mergeCell ref="B40:C40"/>
   </x:mergeCells>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -7213,9 +7213,9 @@
     <x:mergeCell ref="B39:C39"/>
     <x:mergeCell ref="B40:C40"/>
   </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="9" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -193,7 +193,6 @@
       <x:color theme="1"/>
       <x:name val="Tahoma"/>
     </x:font>
-    <x:font/>
     <x:font>
       <x:sz val="10.0"/>
       <x:color theme="1"/>
@@ -220,6 +219,13 @@
       <x:name val="Arial"/>
     </x:font>
     <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
@@ -239,328 +245,93 @@
       <x:patternFill patternType="gray125"/>
     </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="1">
     <x:border/>
-    <x:border>
-      <x:left style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:left>
-      <x:right style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:right>
-      <x:top style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:top>
-      <x:bottom style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:left>
-      <x:top style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:top>
-      <x:bottom style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:top>
-      <x:bottom style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:left>
-      <x:right style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:right>
-      <x:top style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:top>
-      <x:bottom style="medium">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:left>
-      <x:right style="medium">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:top>
-      <x:bottom style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="medium">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:top style="medium">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="medium">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="medium">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="medium">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="medium">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="medium">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="medium">
-        <x:color rgb="FF000000"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:left>
-      <x:right style="medium">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:top>
-      <x:bottom style="medium">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="medium">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="medium">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:bottom style="medium">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:left>
-      <x:right style="medium">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:top>
-      <x:bottom style="double">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:right>
-      <x:top style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:top>
-      <x:bottom style="medium">
-        <x:color rgb="FFCCCCCC"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="4" fontId="4" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="4" fontId="2" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="4" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="4" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="right" wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="right" wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="4" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="right" wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="left" wrapText="1" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="bottom"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -787,9 +558,6 @@
       <x:c r="B1" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="s"/>
-      <x:c r="D1" s="3" t="s"/>
-      <x:c r="E1" s="3" t="s"/>
       <x:c r="F1" s="1" t="s"/>
     </x:row>
     <x:row r="2" spans="1:6" ht="14.25" customHeight="1">
@@ -797,19 +565,16 @@
       <x:c r="B2" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="s"/>
-      <x:c r="D2" s="3" t="s"/>
-      <x:c r="E2" s="3" t="s"/>
       <x:c r="F2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:6" ht="14.25" customHeight="1">
       <x:c r="A3" s="1" t="s"/>
-      <x:c r="B3" s="28" t="s">
+      <x:c r="B3" s="16" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="29" t="s"/>
-      <x:c r="D3" s="29" t="s"/>
-      <x:c r="E3" s="29" t="s"/>
+      <x:c r="C3" s="16" t="s"/>
+      <x:c r="D3" s="16" t="s"/>
+      <x:c r="E3" s="16" t="s"/>
       <x:c r="F3" s="1" t="s"/>
     </x:row>
     <x:row r="4" spans="1:6" ht="14.25" customHeight="1">
@@ -822,7 +587,7 @@
     </x:row>
     <x:row r="5" spans="1:6" ht="14.25" customHeight="1">
       <x:c r="A5" s="1" t="s"/>
-      <x:c r="B5" s="4" t="s">
+      <x:c r="B5" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s"/>
@@ -832,7 +597,7 @@
     </x:row>
     <x:row r="6" spans="1:6" ht="14.25" customHeight="1">
       <x:c r="A6" s="1" t="s"/>
-      <x:c r="B6" s="5" t="s">
+      <x:c r="B6" s="4" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s"/>
@@ -850,303 +615,301 @@
     </x:row>
     <x:row r="8" spans="1:6" ht="14.25" customHeight="1">
       <x:c r="A8" s="1" t="s"/>
-      <x:c r="B8" s="6" t="s"/>
-      <x:c r="C8" s="6" t="s"/>
-      <x:c r="D8" s="6" t="s"/>
-      <x:c r="E8" s="6" t="s"/>
+      <x:c r="B8" s="1" t="s"/>
+      <x:c r="C8" s="1" t="s"/>
+      <x:c r="D8" s="1" t="s"/>
+      <x:c r="E8" s="1" t="s"/>
       <x:c r="F8" s="1" t="s"/>
     </x:row>
     <x:row r="9" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A9" s="7" t="s"/>
-      <x:c r="B9" s="7" t="s"/>
-      <x:c r="C9" s="7" t="s"/>
-      <x:c r="D9" s="8" t="s">
+      <x:c r="A9" s="1" t="s"/>
+      <x:c r="B9" s="1" t="s"/>
+      <x:c r="C9" s="1" t="s"/>
+      <x:c r="D9" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E9" s="9" t="s"/>
       <x:c r="F9" s="1" t="s"/>
     </x:row>
     <x:row r="10" spans="1:6" ht="27" customHeight="1">
-      <x:c r="A10" s="7" t="s"/>
-      <x:c r="B10" s="10" t="s">
+      <x:c r="A10" s="1" t="s"/>
+      <x:c r="B10" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
+      <x:c r="C10" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D10" s="7" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E10" s="12" t="s">
+      <x:c r="E10" s="7" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s"/>
     </x:row>
     <x:row r="11" spans="1:6" ht="17.25" customHeight="1">
-      <x:c r="A11" s="7" t="s"/>
-      <x:c r="B11" s="13" t="s"/>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="A11" s="1" t="s"/>
+      <x:c r="B11" s="1" t="s"/>
+      <x:c r="C11" s="6" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D11" s="14" t="s">
+      <x:c r="D11" s="6" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s"/>
       <x:c r="F11" s="1" t="s"/>
     </x:row>
     <x:row r="12" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A12" s="7" t="s"/>
-      <x:c r="B12" s="10" t="s">
+      <x:c r="A12" s="1" t="s"/>
+      <x:c r="B12" s="5" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C12" s="7" t="s"/>
-      <x:c r="D12" s="7" t="s"/>
-      <x:c r="E12" s="10" t="s"/>
+      <x:c r="C12" s="1" t="s"/>
+      <x:c r="D12" s="1" t="s"/>
+      <x:c r="E12" s="5" t="s"/>
       <x:c r="F12" s="1" t="s"/>
     </x:row>
     <x:row r="13" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A13" s="7" t="s"/>
-      <x:c r="B13" s="10" t="s">
+      <x:c r="A13" s="1" t="s"/>
+      <x:c r="B13" s="5" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="s"/>
-      <x:c r="D13" s="7" t="s"/>
-      <x:c r="E13" s="16" t="n">
+      <x:c r="C13" s="6" t="s"/>
+      <x:c r="D13" s="1" t="s"/>
+      <x:c r="E13" s="8" t="n">
         <x:v>810</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
     <x:row r="14" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A14" s="7" t="s"/>
-      <x:c r="B14" s="10" t="s"/>
-      <x:c r="C14" s="11" t="s"/>
-      <x:c r="D14" s="7" t="s"/>
-      <x:c r="E14" s="7" t="s"/>
+      <x:c r="A14" s="1" t="s"/>
+      <x:c r="B14" s="5" t="s"/>
+      <x:c r="C14" s="6" t="s"/>
+      <x:c r="D14" s="1" t="s"/>
+      <x:c r="E14" s="1" t="s"/>
       <x:c r="F14" s="1" t="s"/>
     </x:row>
     <x:row r="15" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A15" s="7" t="s"/>
-      <x:c r="B15" s="10" t="s">
+      <x:c r="A15" s="1" t="s"/>
+      <x:c r="B15" s="5" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="s">
+      <x:c r="C15" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="n">
+      <x:c r="D15" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="7" t="s"/>
+      <x:c r="E15" s="1" t="s"/>
       <x:c r="F15" s="1" t="s"/>
     </x:row>
     <x:row r="16" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A16" s="7" t="s"/>
-      <x:c r="B16" s="10" t="s">
+      <x:c r="A16" s="1" t="s"/>
+      <x:c r="B16" s="5" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="s">
+      <x:c r="C16" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="n">
+      <x:c r="D16" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="7" t="s"/>
+      <x:c r="E16" s="1" t="s"/>
       <x:c r="F16" s="1" t="s"/>
     </x:row>
     <x:row r="17" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A17" s="7" t="s"/>
-      <x:c r="B17" s="10" t="s">
+      <x:c r="A17" s="1" t="s"/>
+      <x:c r="B17" s="5" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="s">
+      <x:c r="C17" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D17" s="18" t="n">
+      <x:c r="D17" s="10" t="n">
         <x:v>2320</x:v>
       </x:c>
-      <x:c r="E17" s="7" t="s"/>
+      <x:c r="E17" s="1" t="s"/>
       <x:c r="F17" s="1" t="s"/>
     </x:row>
     <x:row r="18" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A18" s="7" t="s"/>
-      <x:c r="B18" s="10" t="s">
+      <x:c r="A18" s="1" t="s"/>
+      <x:c r="B18" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C18" s="17" t="s">
+      <x:c r="C18" s="9" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="n">
+      <x:c r="D18" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="7" t="s"/>
+      <x:c r="E18" s="1" t="s"/>
       <x:c r="F18" s="1" t="s"/>
     </x:row>
     <x:row r="19" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A19" s="7" t="s"/>
-      <x:c r="B19" s="10" t="s">
+      <x:c r="A19" s="1" t="s"/>
+      <x:c r="B19" s="5" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C19" s="17" t="s">
+      <x:c r="C19" s="9" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s"/>
-      <x:c r="E19" s="7" t="s"/>
+      <x:c r="D19" s="8" t="s"/>
+      <x:c r="E19" s="1" t="s"/>
       <x:c r="F19" s="1" t="s"/>
     </x:row>
     <x:row r="20" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A20" s="7" t="s"/>
-      <x:c r="B20" s="10" t="s">
+      <x:c r="A20" s="1" t="s"/>
+      <x:c r="B20" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C20" s="17" t="s">
+      <x:c r="C20" s="9" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="n">
+      <x:c r="D20" s="8" t="n">
         <x:v>22930</x:v>
       </x:c>
-      <x:c r="E20" s="7" t="s"/>
+      <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
     </x:row>
     <x:row r="21" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A21" s="7" t="s"/>
-      <x:c r="B21" s="10" t="s">
+      <x:c r="A21" s="1" t="s"/>
+      <x:c r="B21" s="5" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C21" s="17" t="s">
+      <x:c r="C21" s="9" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="n">
+      <x:c r="D21" s="8" t="n">
         <x:v>29760</x:v>
       </x:c>
-      <x:c r="E21" s="7" t="s"/>
+      <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>
     </x:row>
     <x:row r="22" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A22" s="7" t="s"/>
-      <x:c r="B22" s="10" t="s">
+      <x:c r="A22" s="1" t="s"/>
+      <x:c r="B22" s="5" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D22" s="18" t="s"/>
-      <x:c r="E22" s="7" t="s"/>
+      <x:c r="D22" s="10" t="s"/>
+      <x:c r="E22" s="1" t="s"/>
       <x:c r="F22" s="1" t="s"/>
     </x:row>
     <x:row r="23" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A23" s="7" t="s"/>
-      <x:c r="B23" s="10" t="s">
+      <x:c r="A23" s="1" t="s"/>
+      <x:c r="B23" s="5" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C23" s="17" t="s">
+      <x:c r="C23" s="9" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="s"/>
-      <x:c r="E23" s="7" t="s"/>
+      <x:c r="D23" s="8" t="s"/>
+      <x:c r="E23" s="1" t="s"/>
       <x:c r="F23" s="1" t="s"/>
     </x:row>
     <x:row r="24" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A24" s="7" t="s"/>
-      <x:c r="B24" s="10" t="s">
+      <x:c r="A24" s="1" t="s"/>
+      <x:c r="B24" s="5" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C24" s="17" t="s">
+      <x:c r="C24" s="9" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D24" s="16" t="s"/>
-      <x:c r="E24" s="7" t="s"/>
+      <x:c r="D24" s="8" t="s"/>
+      <x:c r="E24" s="1" t="s"/>
       <x:c r="F24" s="1" t="s"/>
     </x:row>
     <x:row r="25" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A25" s="7" t="s"/>
-      <x:c r="B25" s="10" t="s">
+      <x:c r="A25" s="1" t="s"/>
+      <x:c r="B25" s="5" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C25" s="17" t="s">
+      <x:c r="C25" s="9" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D25" s="18" t="s"/>
-      <x:c r="E25" s="7" t="s"/>
+      <x:c r="D25" s="10" t="s"/>
+      <x:c r="E25" s="1" t="s"/>
       <x:c r="F25" s="1" t="s"/>
     </x:row>
     <x:row r="26" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A26" s="7" t="s"/>
-      <x:c r="B26" s="10" t="s">
+      <x:c r="A26" s="1" t="s"/>
+      <x:c r="B26" s="5" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D26" s="7" t="n">
+      <x:c r="D26" s="1" t="n">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="E26" s="7" t="s"/>
+      <x:c r="E26" s="1" t="s"/>
       <x:c r="F26" s="1" t="s"/>
     </x:row>
     <x:row r="27" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A27" s="7" t="s"/>
-      <x:c r="B27" s="10" t="s">
+      <x:c r="A27" s="1" t="s"/>
+      <x:c r="B27" s="5" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D27" s="18" t="n">
+      <x:c r="D27" s="10" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E27" s="7" t="s"/>
+      <x:c r="E27" s="1" t="s"/>
       <x:c r="F27" s="1" t="s"/>
     </x:row>
     <x:row r="28" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A28" s="7" t="s"/>
-      <x:c r="B28" s="10" t="s">
+      <x:c r="A28" s="1" t="s"/>
+      <x:c r="B28" s="5" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C28" s="17" t="s">
+      <x:c r="C28" s="9" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D28" s="7" t="s"/>
-      <x:c r="E28" s="7" t="s"/>
+      <x:c r="D28" s="1" t="s"/>
+      <x:c r="E28" s="1" t="s"/>
       <x:c r="F28" s="1" t="s"/>
     </x:row>
     <x:row r="29" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A29" s="7" t="s"/>
-      <x:c r="B29" s="10" t="s">
+      <x:c r="A29" s="1" t="s"/>
+      <x:c r="B29" s="5" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C29" s="17" t="s">
+      <x:c r="C29" s="9" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D29" s="16" t="s"/>
-      <x:c r="E29" s="7" t="s"/>
+      <x:c r="D29" s="8" t="s"/>
+      <x:c r="E29" s="1" t="s"/>
       <x:c r="F29" s="1" t="s"/>
     </x:row>
     <x:row r="30" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A30" s="7" t="s"/>
-      <x:c r="B30" s="13" t="s"/>
-      <x:c r="C30" s="13" t="s"/>
-      <x:c r="D30" s="19" t="s"/>
-      <x:c r="E30" s="13" t="s"/>
+      <x:c r="A30" s="1" t="s"/>
+      <x:c r="B30" s="1" t="s"/>
+      <x:c r="C30" s="1" t="s"/>
+      <x:c r="D30" s="5" t="s"/>
+      <x:c r="E30" s="1" t="s"/>
       <x:c r="F30" s="1" t="s"/>
     </x:row>
     <x:row r="31" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A31" s="7" t="s"/>
-      <x:c r="B31" s="11" t="s">
+      <x:c r="A31" s="1" t="s"/>
+      <x:c r="B31" s="6" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C31" s="7" t="s"/>
-      <x:c r="D31" s="20">
+      <x:c r="C31" s="1" t="s"/>
+      <x:c r="D31" s="11">
         <x:f>SUM(D10:D29)</x:f>
       </x:c>
-      <x:c r="E31" s="20">
+      <x:c r="E31" s="11">
         <x:f>SUM(E13)</x:f>
       </x:c>
       <x:c r="F31" s="1" t="s"/>
     </x:row>
     <x:row r="32" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A32" s="7" t="s"/>
-      <x:c r="B32" s="10" t="s"/>
-      <x:c r="C32" s="10" t="s"/>
-      <x:c r="D32" s="21" t="s"/>
-      <x:c r="E32" s="21" t="s"/>
+      <x:c r="A32" s="1" t="s"/>
+      <x:c r="B32" s="5" t="s"/>
+      <x:c r="C32" s="5" t="s"/>
+      <x:c r="D32" s="1" t="s"/>
+      <x:c r="E32" s="1" t="s"/>
       <x:c r="F32" s="1" t="s"/>
     </x:row>
     <x:row r="33" spans="1:6" ht="14.25" customHeight="1">
-      <x:c r="A33" s="7" t="s"/>
-      <x:c r="B33" s="13" t="s"/>
-      <x:c r="C33" s="13" t="s"/>
-      <x:c r="D33" s="19" t="s"/>
-      <x:c r="E33" s="13" t="s"/>
+      <x:c r="A33" s="1" t="s"/>
+      <x:c r="B33" s="1" t="s"/>
+      <x:c r="C33" s="1" t="s"/>
+      <x:c r="D33" s="5" t="s"/>
+      <x:c r="E33" s="1" t="s"/>
       <x:c r="F33" s="1" t="s"/>
     </x:row>
     <x:row r="34" spans="1:6" ht="14.25" customHeight="1">
@@ -1159,11 +922,10 @@
     </x:row>
     <x:row r="35" spans="1:6" ht="14.25" customHeight="1">
       <x:c r="A35" s="1" t="s"/>
-      <x:c r="B35" s="22" t="s">
+      <x:c r="B35" s="12" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C35" s="23" t="s"/>
-      <x:c r="D35" s="24" t="s">
+      <x:c r="D35" s="13" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s"/>
@@ -1171,11 +933,11 @@
     </x:row>
     <x:row r="36" spans="1:6" ht="14.25" customHeight="1">
       <x:c r="A36" s="1" t="s"/>
-      <x:c r="B36" s="25" t="s">
+      <x:c r="B36" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s"/>
-      <x:c r="D36" s="30" t="s">
+      <x:c r="D36" s="17" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s"/>
@@ -1183,11 +945,11 @@
     </x:row>
     <x:row r="37" spans="1:6" ht="14.25" customHeight="1">
       <x:c r="A37" s="1" t="s"/>
-      <x:c r="B37" s="25" t="s">
+      <x:c r="B37" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s"/>
-      <x:c r="D37" s="25" t="s">
+      <x:c r="D37" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s"/>
@@ -1195,11 +957,11 @@
     </x:row>
     <x:row r="38" spans="1:6" ht="26.25" customHeight="1">
       <x:c r="A38" s="1" t="s"/>
-      <x:c r="B38" s="25" t="s">
+      <x:c r="B38" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C38" s="27" t="s"/>
-      <x:c r="D38" s="25" t="s">
+      <x:c r="C38" s="6" t="s"/>
+      <x:c r="D38" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -27,7 +27,7 @@
     <x:t>AND INCOME DEPOSITED WITH THE BUREAU OF TREASURY</x:t>
   </x:si>
   <x:si>
-    <x:t>FOR THE MONTH OF March 2026</x:t>
+    <x:t>FOR THE MONTH OF April 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Department of Information and Communications Technology</x:t>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -27,7 +27,7 @@
     <x:t>AND INCOME DEPOSITED WITH THE BUREAU OF TREASURY</x:t>
   </x:si>
   <x:si>
-    <x:t>FOR THE MONTH OF April 2026</x:t>
+    <x:t>FOR THE MONTH OF May 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Department of Information and Communications Technology</x:t>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>810</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -724,7 +724,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D17" s="10" t="n">
-        <x:v>2320</x:v>
+        <x:v>2380</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s"/>
       <x:c r="F17" s="1" t="s"/>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>22930</x:v>
+        <x:v>23002</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>840</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -724,7 +724,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D17" s="10" t="n">
-        <x:v>2380</x:v>
+        <x:v>3460</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s"/>
       <x:c r="F17" s="1" t="s"/>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>23002</x:v>
+        <x:v>25522</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>870</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>29760</x:v>
+        <x:v>31260</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>900</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>25522</x:v>
+        <x:v>26122</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>31260</x:v>
+        <x:v>33420</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>930</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>33420</x:v>
+        <x:v>34140</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -27,7 +27,7 @@
     <x:t>AND INCOME DEPOSITED WITH THE BUREAU OF TREASURY</x:t>
   </x:si>
   <x:si>
-    <x:t>FOR THE MONTH OF May 2026</x:t>
+    <x:t>FOR THE MONTH OF June 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Department of Information and Communications Technology</x:t>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>960</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -724,7 +724,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D17" s="10" t="n">
-        <x:v>3460</x:v>
+        <x:v>3760</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s"/>
       <x:c r="F17" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>990</x:v>
+        <x:v>1020</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -764,7 +764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="8" t="n">
-        <x:v>26122</x:v>
+        <x:v>26872</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>34140</x:v>
+        <x:v>35640</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>1020</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>35640</x:v>
+        <x:v>37140</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>1050</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>37140</x:v>
+        <x:v>38640</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -27,7 +27,7 @@
     <x:t>AND INCOME DEPOSITED WITH THE BUREAU OF TREASURY</x:t>
   </x:si>
   <x:si>
-    <x:t>FOR THE MONTH OF June 2026</x:t>
+    <x:t>FOR THE MONTH OF July 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Department of Information and Communications Technology</x:t>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>1080</x:v>
+        <x:v>1110</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>38640</x:v>
+        <x:v>40140</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>1110</x:v>
+        <x:v>1140</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>40140</x:v>
+        <x:v>41640</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:III.xlsx
+++ b/reports/excel-reports_cache_report:III.xlsx
@@ -675,7 +675,7 @@
       <x:c r="C13" s="6" t="s"/>
       <x:c r="D13" s="1" t="s"/>
       <x:c r="E13" s="8" t="n">
-        <x:v>1140</x:v>
+        <x:v>1170</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s"/>
     </x:row>
@@ -778,7 +778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="8" t="n">
-        <x:v>41640</x:v>
+        <x:v>43140</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s"/>
       <x:c r="F21" s="1" t="s"/>
